--- a/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -411,16 +411,8 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Beige</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>flipkart</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -430,19 +422,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>shopsy</t>
+          <t>flipkart</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Beige</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>flipkart</t>
+          <t>shopsy</t>
         </is>
       </c>
     </row>
@@ -454,19 +446,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>shopsy</t>
+          <t>flipkart</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Black-baggy</t>
+          <t>Ice</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>flipkart</t>
+          <t>shopsy</t>
         </is>
       </c>
     </row>
@@ -478,19 +470,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>shopsy</t>
+          <t>flipkart</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Black-Plain</t>
+          <t>Black-baggy</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>flipkart</t>
+          <t>shopsy</t>
         </is>
       </c>
     </row>
@@ -502,19 +494,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>shopsy</t>
+          <t>flipkart</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>White-Plain</t>
+          <t>Black-Plain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>flipkart</t>
+          <t>shopsy</t>
         </is>
       </c>
     </row>
@@ -526,19 +518,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>shopsy</t>
+          <t>flipkart</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Trouser</t>
+          <t>White-Plain</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>flipkart</t>
+          <t>shopsy</t>
         </is>
       </c>
     </row>
@@ -549,6 +541,18 @@
         </is>
       </c>
       <c r="B13" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Trouser</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>shopsy</t>
         </is>

--- a/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -409,10 +409,50 @@
           <t>Surface</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -449,6 +489,11 @@
           <t>flipkart</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10-STAR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -545,6 +590,16 @@
           <t>flipkart</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5-IND</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>5-STAR</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -555,6 +610,11 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>shopsy</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>5-IND</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,6 +429,16 @@
           <t>2026-06-19</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -453,6 +463,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -598,6 +618,11 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>5-STAR</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5-GENZ</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,16 @@
           <t>2026-06-20</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -473,6 +483,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -497,6 +517,11 @@
           <t>shopsy</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2-FADE 5-IND</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -514,6 +539,11 @@
           <t>10-STAR</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3-IND</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -640,6 +670,11 @@
       <c r="D14" t="inlineStr">
         <is>
           <t>5-IND</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1-GENZ</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/successful-run-record.xlsx
@@ -2,10 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="360" yWindow="525" windowWidth="19815" windowHeight="7365" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet name="Successful Runs" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -18,13 +22,22 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="1">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -35,6 +48,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -411,42 +425,42 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -505,6 +519,11 @@
           <t>flipkart</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>5-IND</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -517,9 +536,9 @@
           <t>shopsy</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2-FADE 5-IND</t>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10-GENZ</t>
         </is>
       </c>
     </row>
@@ -534,14 +553,9 @@
           <t>flipkart</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>10-STAR</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>3-IND</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>10-FADE</t>
         </is>
       </c>
     </row>
@@ -556,6 +570,16 @@
           <t>shopsy</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10-STAR</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10-FADE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -568,6 +592,11 @@
           <t>flipkart</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4-STAR</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -640,19 +669,9 @@
           <t>flipkart</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>5-IND</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>5-STAR</t>
-        </is>
-      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5-GENZ</t>
+          <t>9-STAR</t>
         </is>
       </c>
     </row>
@@ -667,14 +686,19 @@
           <t>shopsy</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>5-IND</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>1-GENZ</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10-IND</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>14-GENZ</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,16 @@
           <t>2026-06-21</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -493,6 +503,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -673,6 +693,23 @@
         </is>
       </c>
       <c r="I14" t="inlineStr">
+        <is>
+          <t>1-GENZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Track Pant</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>shopsy</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>1-GENZ</t>
         </is>

--- a/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,16 @@
           <t>2026-07-08</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -513,6 +523,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -540,6 +560,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>2-FADE 5-IND</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1-STAR</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,16 @@
           <t>2026-07-09</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -533,6 +543,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -737,6 +757,23 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>1-GENZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Track Pant</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>1-STAR</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/successful-run-record.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>1-STAR</t>
+          <t>2-STAR</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,16 @@
           <t>2026-07-18</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -553,6 +563,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -774,6 +794,23 @@
       <c r="O16" t="inlineStr">
         <is>
           <t>2-STAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>White-Baggy</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>flipkart</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1-STAR</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +489,16 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -573,6 +583,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -585,6 +605,11 @@
           <t>flipkart</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>6-STAR</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -629,6 +654,11 @@
           <t>3-IND</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5-STAR</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -653,6 +683,11 @@
           <t>flipkart</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4-GENZ</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -811,6 +846,11 @@
       <c r="Q17" t="inlineStr">
         <is>
           <t>1-STAR</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>5-GENZ</t>
         </is>
       </c>
     </row>

--- a/Full-LC-AUTO/successful-run-record.xlsx
+++ b/Full-LC-AUTO/successful-run-record.xlsx
@@ -395,7 +395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,16 @@
           <t>2026-08-02</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
@@ -593,6 +603,16 @@
           <t>Seema</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Prabhu</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Seema</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -851,6 +871,11 @@
       <c r="S17" t="inlineStr">
         <is>
           <t>5-GENZ</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>1-STAR</t>
         </is>
       </c>
     </row>
